--- a/NBFC-MF/Borrowers/Pratima_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Pratima_Daily.xlsx
@@ -8291,31 +8291,33 @@
       <c r="K5" s="27"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>46278</v>
+      </c>
+      <c r="B6" s="23">
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="4" t="str">
+      <c r="D6" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="1"/>
+        <v>60.560113502229989</v>
+      </c>
+      <c r="F6" s="4">
         <f>IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),D6-E6,"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="4" t="str">
+        <v>139.43988649777</v>
+      </c>
+      <c r="G6" s="4">
         <f t="shared" ref="G6:G69" si="4">IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),G5-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>19307.116079826741</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="2"/>
+        <v>692.88392017325896</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>13</v>
@@ -8323,31 +8325,33 @@
       <c r="K6" s="27"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A7" s="19">
+        <v>46279</v>
+      </c>
+      <c r="B7" s="24">
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>60.125872325146176</v>
+      </c>
+      <c r="F7" s="21">
         <f t="shared" ref="F7:F70" si="5">IF(AND($A7&lt;&gt;"",$B7&lt;&gt;""),D7-E7,"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>139.87412767485381</v>
+      </c>
+      <c r="G7" s="21">
+        <f t="shared" si="4"/>
+        <v>19167.241952151886</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>832.75804784811407</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>7</v>
@@ -8357,31 +8361,33 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A8" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B8" s="23">
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G8" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H8" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D8" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="1"/>
+        <v>59.690278842028469</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="5"/>
+        <v>140.30972115797152</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" si="4"/>
+        <v>19026.932230993916</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="2"/>
+        <v>973.06776900608384</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>14</v>
@@ -8392,31 +8398,33 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A9" s="19">
+        <v>46281</v>
+      </c>
+      <c r="B9" s="24">
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>59.253328841549859</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="5"/>
+        <v>140.74667115845014</v>
+      </c>
+      <c r="G9" s="21">
+        <f t="shared" si="4"/>
+        <v>18886.185559835467</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>1113.8144401645332</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>8</v>
@@ -8426,31 +8434,33 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A10" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B10" s="23">
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G10" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H10" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D10" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="1"/>
+        <v>58.815018099268443</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="5"/>
+        <v>141.18498190073154</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="4"/>
+        <v>18745.000577934734</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="2"/>
+        <v>1254.9994220652661</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>15</v>
@@ -8460,103 +8470,109 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A11" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B11" s="24">
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>58.375342377586676</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="5"/>
+        <v>141.62465762241334</v>
+      </c>
+      <c r="G11" s="21">
+        <f t="shared" si="4"/>
+        <v>18603.375920312319</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>1396.6240796876809</v>
       </c>
       <c r="J11" s="8"/>
       <c r="L11" s="22"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A12" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B12" s="23">
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G12" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H12" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D12" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" si="1"/>
+        <v>57.934297425710348</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="5"/>
+        <v>142.06570257428965</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="4"/>
+        <v>18461.310217738028</v>
+      </c>
+      <c r="H12" s="4">
+        <f t="shared" si="2"/>
+        <v>1538.6897822619721</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46285</v>
+      </c>
+      <c r="B13" s="24">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>57.491878979607513</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="5"/>
+        <v>142.50812102039248</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="4"/>
+        <v>18318.802096717634</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>1681.1979032823656</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>23200</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -8591,7 +8607,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>19446.555966324511</v>
+        <v>18318.802096717634</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -8626,7 +8642,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>553.44403367548875</v>
+        <v>1681.1979032823656</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Pratima_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Pratima_Daily.xlsx
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -8572,105 +8572,111 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>21600</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B14" s="23">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D14" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="1"/>
+        <v>57.048082761967244</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="5"/>
+        <v>142.95191723803276</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="4"/>
+        <v>18175.850179479603</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" si="2"/>
+        <v>1824.149820520397</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>18318.802096717634</v>
+        <v>17162.643827501808</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46288</v>
+      </c>
+      <c r="B15" s="24">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="1"/>
+        <v>56.602904482158308</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="5"/>
+        <v>143.39709551784171</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="4"/>
+        <v>18032.453083961762</v>
+      </c>
+      <c r="H15" s="21">
+        <f t="shared" si="2"/>
+        <v>1967.5469160382381</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>6</v>
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1681.1979032823656</v>
+        <v>2837.3561724981919</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A16" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B16" s="23">
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D16" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="1"/>
+        <v>56.156339836187634</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="5"/>
+        <v>143.84366016381236</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="4"/>
+        <v>17888.609423797949</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" si="2"/>
+        <v>2111.3905762020513</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -8681,31 +8687,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A17" s="19">
+        <v>46290</v>
+      </c>
+      <c r="B17" s="24">
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D17" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="1"/>
+        <v>55.708384506658753</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="5"/>
+        <v>144.29161549334125</v>
+      </c>
+      <c r="G17" s="21">
+        <f t="shared" si="4"/>
+        <v>17744.317808304608</v>
+      </c>
+      <c r="H17" s="21">
+        <f t="shared" si="2"/>
+        <v>2255.6821916953922</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -8716,117 +8724,125 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A18" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B18" s="23">
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D18" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="1"/>
+        <v>55.259034162730046</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="5"/>
+        <v>144.74096583726995</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="4"/>
+        <v>17599.576842467337</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" si="2"/>
+        <v>2400.423157532663</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A19" s="19">
+        <v>46292</v>
+      </c>
+      <c r="B19" s="24">
+        <f t="shared" si="3"/>
+        <v>18</v>
       </c>
       <c r="C19" s="20"/>
-      <c r="D19" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E19" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F19" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G19" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H19" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D19" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E19" s="21">
+        <f t="shared" si="1"/>
+        <v>54.808284460072834</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="5"/>
+        <v>145.19171553992717</v>
+      </c>
+      <c r="G19" s="21">
+        <f t="shared" si="4"/>
+        <v>17454.385126927409</v>
+      </c>
+      <c r="H19" s="21">
+        <f t="shared" si="2"/>
+        <v>2545.6148730725909</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A20" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B20" s="23">
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E20" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G20" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H20" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D20" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="1"/>
+        <v>54.356131040829446</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="5"/>
+        <v>145.64386895917056</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="4"/>
+        <v>17308.741257968239</v>
+      </c>
+      <c r="H20" s="4">
+        <f t="shared" si="2"/>
+        <v>2691.2587420317614</v>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A21" s="19">
+        <v>46294</v>
+      </c>
+      <c r="B21" s="24">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="C21" s="20"/>
-      <c r="D21" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E21" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F21" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G21" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H21" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D21" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E21" s="21">
+        <f t="shared" si="1"/>
+        <v>53.902569533571032</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="5"/>
+        <v>146.09743046642896</v>
+      </c>
+      <c r="G21" s="21">
+        <f t="shared" si="4"/>
+        <v>17162.643827501808</v>
+      </c>
+      <c r="H21" s="21">
+        <f t="shared" si="2"/>
+        <v>2837.3561724981919</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Pratima_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Pratima_Daily.xlsx
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>20000</v>
+        <v>17600</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>17162.643827501808</v>
+        <v>15373.578293496203</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>2837.3561724981919</v>
+        <v>4626.4217065037974</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -8846,339 +8846,363 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A22" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B22" s="23">
+        <f t="shared" si="3"/>
+        <v>21</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E22" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G22" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D22" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="1"/>
+        <v>53.447595553255304</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="5"/>
+        <v>146.5524044467447</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="4"/>
+        <v>17016.091423055062</v>
+      </c>
+      <c r="H22" s="4">
+        <f t="shared" si="2"/>
+        <v>2983.9085769449375</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A23" s="19">
+        <v>46296</v>
+      </c>
+      <c r="B23" s="24">
+        <f t="shared" si="3"/>
+        <v>22</v>
       </c>
       <c r="C23" s="20"/>
-      <c r="D23" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E23" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F23" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G23" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H23" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D23" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E23" s="21">
+        <f t="shared" si="1"/>
+        <v>52.991204701184181</v>
+      </c>
+      <c r="F23" s="21">
+        <f t="shared" si="5"/>
+        <v>147.00879529881581</v>
+      </c>
+      <c r="G23" s="21">
+        <f t="shared" si="4"/>
+        <v>16869.082627756248</v>
+      </c>
+      <c r="H23" s="21">
+        <f t="shared" si="2"/>
+        <v>3130.9173722437517</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A24" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B24" s="23">
+        <f t="shared" si="3"/>
+        <v>23</v>
       </c>
       <c r="C24" s="3"/>
-      <c r="D24" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E24" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F24" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G24" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H24" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D24" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" si="1"/>
+        <v>52.533392564961225</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="5"/>
+        <v>147.46660743503878</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="4"/>
+        <v>16721.616020321209</v>
+      </c>
+      <c r="H24" s="4">
+        <f t="shared" si="2"/>
+        <v>3278.3839796787906</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A25" s="19">
+        <v>46298</v>
+      </c>
+      <c r="B25" s="24">
+        <f t="shared" si="3"/>
+        <v>24</v>
       </c>
       <c r="C25" s="20"/>
-      <c r="D25" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E25" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F25" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G25" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H25" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D25" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E25" s="21">
+        <f t="shared" si="1"/>
+        <v>52.07415471844898</v>
+      </c>
+      <c r="F25" s="21">
+        <f t="shared" si="5"/>
+        <v>147.92584528155101</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="4"/>
+        <v>16573.690175039657</v>
+      </c>
+      <c r="H25" s="21">
+        <f t="shared" si="2"/>
+        <v>3426.3098249603427</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A26" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B26" s="23">
+        <f t="shared" si="3"/>
+        <v>25</v>
       </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E26" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G26" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H26" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D26" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" si="1"/>
+        <v>51.613486721726204</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="5"/>
+        <v>148.38651327827381</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="4"/>
+        <v>16425.303661761383</v>
+      </c>
+      <c r="H26" s="4">
+        <f t="shared" si="2"/>
+        <v>3574.6963382386166</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A27" s="19">
+        <v>46300</v>
+      </c>
+      <c r="B27" s="24">
+        <f t="shared" si="3"/>
+        <v>26</v>
       </c>
       <c r="C27" s="20"/>
-      <c r="D27" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E27" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F27" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G27" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H27" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D27" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E27" s="21">
+        <f t="shared" si="1"/>
+        <v>51.151384121044934</v>
+      </c>
+      <c r="F27" s="21">
+        <f t="shared" si="5"/>
+        <v>148.84861587895506</v>
+      </c>
+      <c r="G27" s="21">
+        <f t="shared" si="4"/>
+        <v>16276.455045882429</v>
+      </c>
+      <c r="H27" s="21">
+        <f t="shared" si="2"/>
+        <v>3723.5449541175713</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A28" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B28" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E28" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G28" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H28" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D28" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" si="1"/>
+        <v>50.687842448787421</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="5"/>
+        <v>149.31215755121258</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="4"/>
+        <v>16127.142888331216</v>
+      </c>
+      <c r="H28" s="4">
+        <f t="shared" si="2"/>
+        <v>3872.8571116687835</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A29" s="19">
+        <v>46302</v>
+      </c>
+      <c r="B29" s="24">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E29" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F29" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G29" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H29" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D29" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E29" s="21">
+        <f t="shared" si="1"/>
+        <v>50.222857223422949</v>
+      </c>
+      <c r="F29" s="21">
+        <f t="shared" si="5"/>
+        <v>149.77714277657705</v>
+      </c>
+      <c r="G29" s="21">
+        <f t="shared" si="4"/>
+        <v>15977.36574555464</v>
+      </c>
+      <c r="H29" s="21">
+        <f t="shared" si="2"/>
+        <v>4022.6342544453601</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A30" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B30" s="23">
+        <f t="shared" si="3"/>
+        <v>29</v>
       </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E30" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G30" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H30" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D30" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E30" s="4">
+        <f t="shared" si="1"/>
+        <v>49.756423949464491</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="5"/>
+        <v>150.24357605053552</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="4"/>
+        <v>15827.122169504104</v>
+      </c>
+      <c r="H30" s="4">
+        <f t="shared" si="2"/>
+        <v>4172.877830495896</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A31" s="19">
+        <v>46304</v>
+      </c>
+      <c r="B31" s="24">
+        <f t="shared" si="3"/>
+        <v>30</v>
       </c>
       <c r="C31" s="20"/>
-      <c r="D31" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E31" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F31" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G31" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H31" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D31" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E31" s="21">
+        <f t="shared" si="1"/>
+        <v>49.288538117425247</v>
+      </c>
+      <c r="F31" s="21">
+        <f t="shared" si="5"/>
+        <v>150.71146188257475</v>
+      </c>
+      <c r="G31" s="21">
+        <f t="shared" si="4"/>
+        <v>15676.41070762153</v>
+      </c>
+      <c r="H31" s="21">
+        <f t="shared" si="2"/>
+        <v>4323.5892923784704</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A32" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B32" s="23">
+        <f t="shared" si="3"/>
+        <v>31</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E32" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G32" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H32" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D32" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E32" s="4">
+        <f t="shared" si="1"/>
+        <v>48.819195203775088</v>
+      </c>
+      <c r="F32" s="4">
+        <f t="shared" si="5"/>
+        <v>151.18080479622492</v>
+      </c>
+      <c r="G32" s="4">
+        <f t="shared" si="4"/>
+        <v>15525.229902825306</v>
+      </c>
+      <c r="H32" s="4">
+        <f t="shared" si="2"/>
+        <v>4474.7700971746945</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="B33" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A33" s="19">
+        <v>46307</v>
+      </c>
+      <c r="B33" s="24">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="C33" s="20"/>
-      <c r="D33" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E33" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G33" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H33" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D33" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E33" s="21">
+        <f t="shared" si="1"/>
+        <v>48.348390670896748</v>
+      </c>
+      <c r="F33" s="21">
+        <f t="shared" si="5"/>
+        <v>151.65160932910325</v>
+      </c>
+      <c r="G33" s="21">
+        <f t="shared" si="4"/>
+        <v>15373.578293496203</v>
+      </c>
+      <c r="H33" s="21">
+        <f t="shared" si="2"/>
+        <v>4626.4217065037974</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
